--- a/data/microdegree_info.xlsx
+++ b/data/microdegree_info.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\20260915_chat-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6361D078-C70C-4C49-841A-134C2F81D737}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F8CD11-89AB-4793-9627-2EC31AB9880A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="9750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="298">
   <si>
     <t>제도유형</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5524,12 +5524,84 @@
     <t>제2공학관 205호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>정신건강 사회복지 MD</t>
+  </si>
+  <si>
+    <t>커뮤니티 케어 MD</t>
+  </si>
+  <si>
+    <t>식생활안전관리 MD</t>
+  </si>
+  <si>
+    <t>GX 융합디자이너 MD</t>
+  </si>
+  <si>
+    <t>평캠 인학관 513호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-610-4780</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신건강, 사회, 복지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합돌봄, 돌봄, 초고령, 복지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급식, 식품산업, 양양, 위생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식품영양, 영양학, 식생활관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품, 공간, 공공디자인, 디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신건강에 대한 깊은 이해를 바탕으로 위기 상황에 처한 대상자 발굴 및 체계적인 사례관리를 통해 사회 복귀를 돕는 실무 전문가 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역사회 내 보건복지 자원을 연계하여 노인/장애인 대상 사례관리를 수행할 수 있는 실무 혁신 인재 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영양교육 및 상담, 단체급식 운영과 식생활 안전에 대한 이론과 실무능력을 바탕으로 건강증진과 질병 예방에 기여할 수 있는 실무형 전문인재 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영양학적 지식을 바탕으로 이를 현대 사회의 식생활 환경에 적용하고, 나아가 신기술 및 시각적 가치와 결합하는 융복합 전문 인재 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역기반산업(GX)의 변화와 산업수요에 대응할 수 있는 제품공간 공공디자인 기반의 융합형 실무 인재 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평캠 인학관 513호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스마트영양관리 MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사회복지학전공(평캠)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5565,6 +5637,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5602,7 +5682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5633,6 +5713,9 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -7385,39 +7468,134 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57"/>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="G57"/>
+      <c r="A57" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58"/>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="G58"/>
+      <c r="A58" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="G59"/>
+      <c r="A59" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="G60"/>
+      <c r="A60" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61"/>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="G61"/>
+      <c r="A61" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62"/>
